--- a/fixtures/estadocuenta-sintetico.xlsx
+++ b/fixtures/estadocuenta-sintetico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,30 +674,62 @@
         <v>600000</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>VIST</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D24" t="n">
+        <v>100000</v>
+      </c>
+    </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TOTALES</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Total ARS</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>24000000</v>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D25" t="n">
+        <v>100000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>TOTALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Total ARS</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>24200000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Total USD</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B29" t="n">
         <v>20000</v>
       </c>
     </row>
